--- a/chapters/collection/sensor_telemetry.xlsx
+++ b/chapters/collection/sensor_telemetry.xlsx
@@ -1614,7 +1614,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Notes for the analyst</t>
+          <t>Notes for the analyst (a realistic teaching dataset written for the book)</t>
         </is>
       </c>
     </row>
@@ -1628,14 +1628,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>One row per machine per time interval (a time series). No human enters these values.</t>
+          <t>One row per reading (machine and time), a time series. No human enters these values.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Design: sampling cadence (here 1/min), sensor CALIBRATION &amp; drift control, and clock sync across machines.</t>
+          <t>Design: sampling cadence (here one reading per minute across the line, so each machine is read every few minutes), sensor CALIBRATION &amp; drift control, and clock sync across machines.</t>
         </is>
       </c>
     </row>
